--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486799_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486799_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.9771</v>
+        <v>4.3081</v>
       </c>
       <c r="E2" t="n">
-        <v>2.909</v>
+        <v>3.1159</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0681</v>
+        <v>1.1922</v>
       </c>
       <c r="G2" t="n">
         <v>2.3741</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.3515</v>
+        <v>-1.0205</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.607</v>
+        <v>-0.4002</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.6203</v>
       </c>
       <c r="V2" t="n">
         <v>2.3752</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>I. IBAÑEZ ZAMALLOA</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.3203</v>
+        <v>3.0501</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7355</v>
+        <v>0.8716</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5848</v>
+        <v>2.1785</v>
       </c>
       <c r="G3" t="n">
-        <v>-2.2792</v>
+        <v>2.9398</v>
       </c>
       <c r="H3" t="n">
-        <v>0.42</v>
+        <v>2.0965</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.6992</v>
+        <v>0.8433</v>
       </c>
       <c r="J3" t="n">
-        <v>-1.0706</v>
+        <v>2.3752</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5246</v>
+        <v>1.9591</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.5951</v>
+        <v>0.4161</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.2086</v>
+        <v>0.5646</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1046</v>
+        <v>0.1374</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1041</v>
+        <v>0.4272</v>
       </c>
       <c r="P3" t="n">
-        <v>2.7031</v>
+        <v>1.1585</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7031</v>
+        <v>2.1239</v>
       </c>
       <c r="S3" t="n">
-        <v>1.9143</v>
+        <v>-1.0482</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5784</v>
+        <v>-0.5382</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3359</v>
+        <v>-0.51</v>
       </c>
       <c r="V3" t="n">
-        <v>0.9822</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2455</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>I. IBAÑEZ ZAMALLOA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.5701</v>
+        <v>2.0542</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6647999999999999</v>
+        <v>0.115</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9053</v>
+        <v>1.9392</v>
       </c>
       <c r="G4" t="n">
-        <v>2.9398</v>
+        <v>-2.2792</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0965</v>
+        <v>0.42</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8433</v>
+        <v>-2.6992</v>
       </c>
       <c r="J4" t="n">
-        <v>2.3752</v>
+        <v>-1.0706</v>
       </c>
       <c r="K4" t="n">
-        <v>1.9591</v>
+        <v>1.5246</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4161</v>
+        <v>-2.5951</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5646</v>
+        <v>-1.2086</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1374</v>
+        <v>-1.1046</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4272</v>
+        <v>-0.1041</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>2.7031</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.1239</v>
+        <v>2.7031</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.5282</v>
+        <v>0.6481</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.745</v>
+        <v>-0.0421</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.7832</v>
+        <v>0.6903</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.9822</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2455</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.663</v>
+        <v>1.0106</v>
       </c>
       <c r="E5" t="n">
         <v>0.1113</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5517</v>
+        <v>0.8994</v>
       </c>
       <c r="G5" t="n">
         <v>0.5488</v>
@@ -844,13 +844,13 @@
         <v>1.7377</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.0924</v>
+        <v>-0.7447</v>
       </c>
       <c r="T5" t="n">
         <v>-0.2211</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.8713</v>
+        <v>-0.5236</v>
       </c>
       <c r="V5" t="n">
         <v>-0.5311</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1406</v>
+        <v>-0.1159</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1312</v>
+        <v>-0.0756</v>
       </c>
       <c r="F6" t="n">
-        <v>0.009299999999999999</v>
+        <v>-0.0403</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9723000000000001</v>
@@ -922,13 +922,13 @@
         <v>0.5792</v>
       </c>
       <c r="S6" t="n">
-        <v>0.6564</v>
+        <v>0.3999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4963</v>
+        <v>0.2894</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1601</v>
+        <v>0.1104</v>
       </c>
       <c r="V6" t="n">
         <v>-0.1228</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.622</v>
+        <v>-0.5723</v>
       </c>
       <c r="E7" t="n">
         <v>-0.7792</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1572</v>
+        <v>0.2068</v>
       </c>
       <c r="G7" t="n">
         <v>-0.462</v>
@@ -1000,13 +1000,13 @@
         <v>0.1931</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.353</v>
+        <v>-0.3034</v>
       </c>
       <c r="T7" t="n">
         <v>-0.1104</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2427</v>
+        <v>-0.193</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>P. BALLESPIN DE LA PEÑA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8996</v>
+        <v>-1.2817</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0591</v>
+        <v>-0.8818</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.8405</v>
+        <v>-0.3999</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.8344</v>
+        <v>-0.0513</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6069</v>
+        <v>0.7445000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.2275</v>
+        <v>-0.7957</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6754</v>
+        <v>1.0259</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0141</v>
+        <v>1.7108</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6895</v>
+        <v>-0.6849</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.159</v>
+        <v>-1.0772</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6209</v>
+        <v>-0.9664</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5381</v>
+        <v>-0.1108</v>
       </c>
       <c r="P8" t="n">
-        <v>0.3862</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3862</v>
+        <v>1.5446</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4908</v>
+        <v>0.2206</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3307</v>
+        <v>-0.2625</v>
       </c>
       <c r="U8" t="n">
-        <v>0.16</v>
+        <v>0.4831</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.9421</v>
+        <v>-1.0648</v>
       </c>
       <c r="W8" t="n">
         <v>0.2856</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2277</v>
+        <v>-1.3505</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. BALLESPIN DE LA PEÑA</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1257</v>
+        <v>-1.9285</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.5023</v>
+        <v>-0.1625</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.6234</v>
+        <v>-1.766</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0513</v>
+        <v>-1.8344</v>
       </c>
       <c r="H9" t="n">
-        <v>0.7445000000000001</v>
+        <v>-0.6069</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7957</v>
+        <v>-1.2275</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0259</v>
+        <v>-0.6754</v>
       </c>
       <c r="K9" t="n">
-        <v>1.7108</v>
+        <v>0.0141</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6849</v>
+        <v>-0.6895</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.0772</v>
+        <v>-1.159</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9664</v>
+        <v>-0.6209</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1108</v>
+        <v>-0.5381</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.3862</v>
+        <v>0.3862</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9308</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6234</v>
+        <v>0.4618</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.883</v>
+        <v>0.2273</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2596</v>
+        <v>0.2345</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0648</v>
+        <v>-0.9421</v>
       </c>
       <c r="W9" t="n">
         <v>0.2856</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3505</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.5185</v>
+        <v>-2.5267</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1137</v>
+        <v>-2.3205</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.4048</v>
+        <v>-0.2062</v>
       </c>
       <c r="G10" t="n">
         <v>-2.0824</v>
@@ -1234,13 +1234,13 @@
         <v>1.3515</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7228</v>
+        <v>-0.731</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.0279</v>
+        <v>-0.2347</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6949</v>
+        <v>-0.4963</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0648</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.6183</v>
+        <v>-3.6473</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.3651</v>
+        <v>-2.4685</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2532</v>
+        <v>-1.1787</v>
       </c>
       <c r="G11" t="n">
         <v>-2.3174</v>
@@ -1312,13 +1312,13 @@
         <v>0.3862</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6288</v>
+        <v>0.5999</v>
       </c>
       <c r="T11" t="n">
-        <v>0.11</v>
+        <v>0.0066</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5188</v>
+        <v>0.5933</v>
       </c>
       <c r="V11" t="n">
         <v>-1.3505</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.7979</v>
+        <v>-4.1622</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.0729</v>
+        <v>-4.866</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2749</v>
+        <v>0.7038</v>
       </c>
       <c r="G12" t="n">
         <v>-3.4975</v>
@@ -1390,13 +1390,13 @@
         <v>1.1585</v>
       </c>
       <c r="S12" t="n">
-        <v>1.2745</v>
+        <v>0.9102</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3866</v>
+        <v>-0.1798</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6611</v>
+        <v>1.09</v>
       </c>
       <c r="V12" t="n">
         <v>0.1628</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.3344</v>
+        <v>-4.4337</v>
       </c>
       <c r="E13" t="n">
         <v>-5.5989</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2645</v>
+        <v>1.1652</v>
       </c>
       <c r="G13" t="n">
         <v>-1.2618</v>
@@ -1468,13 +1468,13 @@
         <v>0.7723</v>
       </c>
       <c r="S13" t="n">
-        <v>0.0166</v>
+        <v>-0.0827</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3311</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3477</v>
+        <v>0.2484</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-8.245299999999999</v>
+        <v>-8.2453</v>
       </c>
       <c r="E14" t="n">
-        <v>-12.9394</v>
+        <v>-12.9392</v>
       </c>
       <c r="F14" t="n">
-        <v>4.6939</v>
+        <v>4.694000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>-8.895600000000002</v>
@@ -1519,7 +1519,7 @@
         <v>-11.6533</v>
       </c>
       <c r="J14" t="n">
-        <v>-4.9547</v>
+        <v>-4.954700000000001</v>
       </c>
       <c r="K14" t="n">
         <v>6.901800000000001</v>
@@ -1546,19 +1546,19 @@
         <v>14.4809</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6899000000000004</v>
+        <v>-0.6900000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7967</v>
+        <v>-1.7968</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1066</v>
+        <v>1.1068</v>
       </c>
       <c r="V14" t="n">
-        <v>-1.555899999999999</v>
+        <v>-1.5559</v>
       </c>
       <c r="W14" t="n">
-        <v>5.396699999999999</v>
+        <v>5.3967</v>
       </c>
       <c r="X14" t="n">
         <v>-6.9529</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>11.501</v>
+        <v>11.763</v>
       </c>
       <c r="E15" t="n">
         <v>10.1367</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3642</v>
+        <v>1.6263</v>
       </c>
       <c r="G15" t="n">
         <v>7.8455</v>
@@ -1624,13 +1624,13 @@
         <v>1.7377</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.6068</v>
+        <v>-0.3448</v>
       </c>
       <c r="T15" t="n">
         <v>-0.4142</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1927</v>
+        <v>0.0694</v>
       </c>
       <c r="V15" t="n">
         <v>3.6831</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.9213</v>
+        <v>2.8798</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.5468</v>
+        <v>-1.3399</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4681</v>
+        <v>4.2197</v>
       </c>
       <c r="G16" t="n">
         <v>0.1211</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>0.0279</v>
+        <v>-0.0136</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.7725</v>
+        <v>-0.5657</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8004</v>
+        <v>0.5521</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.547</v>
+        <v>2.7249</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.095</v>
+        <v>0.008399999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.642</v>
+        <v>2.7165</v>
       </c>
       <c r="G17" t="n">
         <v>2.718</v>
@@ -1780,13 +1780,13 @@
         <v>1.3515</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5571</v>
+        <v>-0.3792</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.607</v>
+        <v>-0.5036</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0499</v>
+        <v>0.1244</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.2081</v>
+        <v>1.6965</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.3961</v>
+        <v>-1.12</v>
       </c>
       <c r="F18" t="n">
-        <v>2.6041</v>
+        <v>2.8165</v>
       </c>
       <c r="G18" t="n">
         <v>3.6717</v>
@@ -1858,13 +1858,13 @@
         <v>1.9308</v>
       </c>
       <c r="S18" t="n">
-        <v>0.4358</v>
+        <v>-0.0757</v>
       </c>
       <c r="T18" t="n">
-        <v>0.3857</v>
+        <v>-0.3383</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0501</v>
+        <v>0.2625</v>
       </c>
       <c r="V18" t="n">
         <v>-1.5133</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.187</v>
+        <v>0.1922</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7436</v>
+        <v>0.847</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9306</v>
+        <v>-0.6548</v>
       </c>
       <c r="G19" t="n">
         <v>0.443</v>
@@ -1936,13 +1936,13 @@
         <v>0.5792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0275</v>
+        <v>0.3517</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0279</v>
+        <v>0.0755</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0004</v>
+        <v>0.2761</v>
       </c>
       <c r="V19" t="n">
         <v>0.9421</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0912</v>
+        <v>-0.7465000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1813</v>
+        <v>1.3882</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2725</v>
+        <v>-2.1346</v>
       </c>
       <c r="G20" t="n">
         <v>0.1436</v>
@@ -2014,13 +2014,13 @@
         <v>0.3862</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2206</v>
+        <v>0.5653</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0825</v>
+        <v>0.2893</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1381</v>
+        <v>0.276</v>
       </c>
       <c r="V20" t="n">
         <v>-1.8415</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.5881</v>
+        <v>-0.9161</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.9025</v>
+        <v>-3.4186</v>
       </c>
       <c r="F21" t="n">
-        <v>3.3144</v>
+        <v>2.5025</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.6239</v>
+        <v>0.8807</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.6826</v>
+        <v>1.5792</v>
       </c>
       <c r="I21" t="n">
-        <v>3.0587</v>
+        <v>-0.6985</v>
       </c>
       <c r="J21" t="n">
-        <v>-3.312</v>
+        <v>-0.3663</v>
       </c>
       <c r="K21" t="n">
-        <v>-3.1991</v>
+        <v>2.2695</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1129</v>
+        <v>-2.6358</v>
       </c>
       <c r="M21" t="n">
-        <v>2.6881</v>
+        <v>1.247</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.4835</v>
+        <v>-0.6903</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1716</v>
+        <v>1.9373</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5792</v>
+        <v>-2.51</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.3515</v>
+        <v>-3.2823</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9308</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6012999999999999</v>
+        <v>0.4276</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5245</v>
+        <v>-0.0555</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.07679999999999999</v>
+        <v>0.4831</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.9421</v>
+        <v>0.2856</v>
       </c>
       <c r="W21" t="n">
         <v>0.2856</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.8951</v>
+        <v>-1.1522</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.246</v>
+        <v>-4.9025</v>
       </c>
       <c r="F22" t="n">
-        <v>2.3509</v>
+        <v>3.7503</v>
       </c>
       <c r="G22" t="n">
-        <v>0.8807</v>
+        <v>-0.6239</v>
       </c>
       <c r="H22" t="n">
-        <v>1.5792</v>
+        <v>-3.6826</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6985</v>
+        <v>3.0587</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3663</v>
+        <v>-3.312</v>
       </c>
       <c r="K22" t="n">
-        <v>2.2695</v>
+        <v>-3.1991</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.6358</v>
+        <v>-0.1129</v>
       </c>
       <c r="M22" t="n">
-        <v>1.247</v>
+        <v>2.6881</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.6903</v>
+        <v>-0.4835</v>
       </c>
       <c r="O22" t="n">
-        <v>1.9373</v>
+        <v>3.1716</v>
       </c>
       <c r="P22" t="n">
-        <v>-2.51</v>
+        <v>0.5792</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.2823</v>
+        <v>-1.3515</v>
       </c>
       <c r="R22" t="n">
-        <v>0.7723</v>
+        <v>1.9308</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5514</v>
+        <v>-0.1654</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8829</v>
+        <v>-0.5245</v>
       </c>
       <c r="U22" t="n">
-        <v>0.3315</v>
+        <v>0.3591</v>
       </c>
       <c r="V22" t="n">
-        <v>0.2856</v>
+        <v>-0.9421</v>
       </c>
       <c r="W22" t="n">
         <v>0.2856</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.091</v>
+        <v>-1.5242</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.896</v>
+        <v>-1.3789</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.1949</v>
+        <v>-0.1453</v>
       </c>
       <c r="G23" t="n">
         <v>-1.7379</v>
@@ -2248,13 +2248,13 @@
         <v>0.5792</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0331</v>
+        <v>0.5999</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2759</v>
+        <v>0.2412</v>
       </c>
       <c r="U23" t="n">
-        <v>0.309</v>
+        <v>0.3587</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.0796</v>
+        <v>-5.2932</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.6732</v>
+        <v>-4.9142</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.4065</v>
+        <v>-0.379</v>
       </c>
       <c r="G24" t="n">
         <v>-4.5662</v>
@@ -2326,13 +2326,13 @@
         <v>0.5792</v>
       </c>
       <c r="S24" t="n">
-        <v>2.3168</v>
+        <v>1.1032</v>
       </c>
       <c r="T24" t="n">
-        <v>1.9302</v>
+        <v>0.6891</v>
       </c>
       <c r="U24" t="n">
-        <v>0.3866</v>
+        <v>0.4141</v>
       </c>
       <c r="V24" t="n">
         <v>-0.2856</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>8.2454</v>
+        <v>9.624200000000002</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.693999999999999</v>
+        <v>-4.6938</v>
       </c>
       <c r="F25" t="n">
-        <v>12.9392</v>
+        <v>14.3181</v>
       </c>
       <c r="G25" t="n">
         <v>8.895600000000002</v>
@@ -2404,13 +2404,13 @@
         <v>11.5846</v>
       </c>
       <c r="S25" t="n">
-        <v>0.6901000000000004</v>
+        <v>2.069</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.1065</v>
+        <v>-1.1067</v>
       </c>
       <c r="U25" t="n">
-        <v>1.7965</v>
+        <v>3.1755</v>
       </c>
       <c r="V25" t="n">
         <v>1.556</v>
